--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121147167</v>
       </c>
       <c r="B2" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121147167</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121147167</v>
       </c>
       <c r="B2" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,200 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125923620</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98349</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kälarne, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>559322</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6979919</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125923631</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98245</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ilvåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>559324</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6979919</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125923620</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125923631</v>
       </c>
       <c r="B4" t="n">
-        <v>98245</v>
+        <v>98248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125923620</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125923631</v>
       </c>
       <c r="B4" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125923620</v>
       </c>
       <c r="B3" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125923631</v>
       </c>
       <c r="B4" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125923620</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125923631</v>
       </c>
       <c r="B4" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125923620</v>
       </c>
       <c r="B3" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125923631</v>
       </c>
       <c r="B4" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125923620</v>
       </c>
       <c r="B3" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125923631</v>
       </c>
       <c r="B4" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125923620</v>
       </c>
       <c r="B3" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125923631</v>
       </c>
       <c r="B4" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125923620</v>
       </c>
       <c r="B3" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125923631</v>
       </c>
       <c r="B4" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125923620</v>
       </c>
       <c r="B3" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125923631</v>
       </c>
       <c r="B4" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125923620</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125923631</v>
       </c>
       <c r="B4" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125923620</v>
       </c>
       <c r="B3" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125923631</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>121147167</v>
       </c>
       <c r="B2" t="n">
-        <v>79688</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125923620</v>
+        <v>125923631</v>
       </c>
       <c r="B3" t="n">
-        <v>98382</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,31 +783,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kälarne, Jmt</t>
+          <t>Ilvåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559322</v>
+        <v>559324</v>
       </c>
       <c r="R3" t="n">
         <v>6979919</v>
@@ -874,48 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125923631</v>
+        <v>98560702</v>
       </c>
       <c r="B4" t="n">
-        <v>98278</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ilvåsen, Jmt</t>
+          <t>Midsommarberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559324</v>
+        <v>559355</v>
       </c>
       <c r="R4" t="n">
-        <v>6979919</v>
+        <v>6979978</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -939,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -959,15 +954,116 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eva Romell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter på asp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125923620</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kälarne, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>559322</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6979919</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47183-2023 artfynd.xlsx
+++ b/artfynd/A 47183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121147167</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125923631</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
           <t>Åtgärdsprogram för hotade arter på asp</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98560702</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,8 +1084,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125923620</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>